--- a/Result/profitability/1522.xlsx
+++ b/Result/profitability/1522.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.22</v>
       </c>
       <c r="M2" t="n">
-        <v>0.35625</v>
+        <v>0.12125</v>
       </c>
       <c r="N2" t="n">
-        <v>22.16</v>
+        <v>20.84625</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.45</v>
       </c>
       <c r="M3" t="n">
-        <v>0.25</v>
+        <v>0.2025</v>
       </c>
       <c r="N3" t="n">
-        <v>21.735</v>
+        <v>20.49</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>0.47</v>
       </c>
       <c r="M4" t="n">
-        <v>0.33375</v>
+        <v>0.08750000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>20.54125</v>
+        <v>19.055</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>0.11</v>
+        <v>0.19875</v>
       </c>
       <c r="N5" t="n">
-        <v>18.735</v>
+        <v>18.525</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3575</v>
+        <v>0.15125</v>
       </c>
       <c r="N6" t="n">
-        <v>19.07</v>
+        <v>18.09375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1149,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.29</v>
       </c>
       <c r="M7" t="n">
-        <v>0.26</v>
+        <v>0.11875</v>
       </c>
       <c r="N7" t="n">
-        <v>18.415</v>
+        <v>18.7825</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.43</v>
       </c>
       <c r="M8" t="n">
-        <v>0.245</v>
+        <v>0.19625</v>
       </c>
       <c r="N8" t="n">
-        <v>18.675</v>
+        <v>18.98625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.23</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3124999999999999</v>
+        <v>0.3125</v>
       </c>
       <c r="N11" t="n">
         <v>18.89125</v>
@@ -2026,7 +2026,7 @@
         <v>-0.02</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3074999999999999</v>
+        <v>0.3075000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>18.89</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1522</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6670</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5471</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1199</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-21</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.31%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-95</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-115</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-119</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.5225</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.052631578947368</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.489999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1608527131782944</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.7100000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.5503875968992249</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.08549618320610686</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
